--- a/artfynd/A 60471-2025 artfynd.xlsx
+++ b/artfynd/A 60471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90707612</v>
+        <v>100237732</v>
       </c>
       <c r="B2" t="n">
-        <v>81962</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>232272</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergs säteri, Berg, sydväst om Lammhult, Växjö kommun, Sm, Sm</t>
+          <t>Alet, Ödekyrkogården, Berg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483059.7446006797</v>
+        <v>483054</v>
       </c>
       <c r="R2" t="n">
-        <v>6325233.069085723</v>
+        <v>6325189</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,43 +776,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>alkärr</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Annchristin Nyström</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annchristin Nyström</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115326974</v>
+        <v>109077643</v>
       </c>
       <c r="B3" t="n">
-        <v>83044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,40 +805,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>232272</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergs säteri, Sm</t>
+          <t>Alet, Ödekyrkogården, Berg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483056</v>
+        <v>483054</v>
       </c>
       <c r="R3" t="n">
-        <v>6325241</v>
+        <v>6325189</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,12 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,11 +894,6 @@
       </c>
       <c r="AE3" t="b">
         <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -907,6 +910,340 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131679655</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alet, Ödekyrkogården, Berg, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483054</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6325189</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>90707612</v>
+      </c>
+      <c r="B5" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergs säteri, Berg, sydväst om Lammhult, Växjö kommun, Sm, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483060</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6325233</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-02-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-02-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>alkärr</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annchristin Nyström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annchristin Nyström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115326974</v>
+      </c>
+      <c r="B6" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergs säteri, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483056</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6325241</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60471-2025 artfynd.xlsx
+++ b/artfynd/A 60471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100237732</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109077643</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131679655</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90707612</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,8 +1269,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115326974</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>